--- a/Desafio 4 - Vale Refeição/Desafio 4 - Dados/BASE SINDICATO X VALOR.xlsx
+++ b/Desafio 4 - Vale Refeição/Desafio 4 - Dados/BASE SINDICATO X VALOR.xlsx
@@ -1,23 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Meu Drive\Cursos e Treinamentos\Cientista de Dados\Treinamento Python\I2A2\Desafios\Desafio 4 - Vale Refeição\Desafio 4 - Dados\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\thais.agne\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9ED54A36-330D-43D0-8669-E01CDFB8C83C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A5ACCD5E-3A5E-4BAA-A3CB-47479A88C45E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{ACAACFC3-E98F-40BF-9B32-1921B65F1066}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{ACAACFC3-E98F-40BF-9B32-1921B65F1066}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$B$6</definedName>
-  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -34,9 +31,6 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
@@ -72,7 +66,7 @@
   <numFmts count="1">
     <numFmt numFmtId="8" formatCode="&quot;R$&quot;\ #,##0.00;[Red]\-&quot;R$&quot;\ #,##0.00"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -507,11 +501,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{567EE969-C8CC-4648-B0E1-A81E0D083ADD}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultColWidth="14.125" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="14.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:2" ht="21.75" thickBot="1">
+    <row r="1" spans="1:2" ht="23.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -519,7 +512,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="15" hidden="1" thickBot="1">
+    <row r="2" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
@@ -527,7 +520,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="15" hidden="1" thickBot="1">
+    <row r="3" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="4" t="s">
         <v>3</v>
       </c>
@@ -535,7 +528,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="15" hidden="1" thickBot="1">
+    <row r="4" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="2" t="s">
         <v>4</v>
       </c>
@@ -543,7 +536,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="15" thickBot="1">
+    <row r="5" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="4" t="s">
         <v>5</v>
       </c>
@@ -551,19 +544,12 @@
         <v>37.5</v>
       </c>
     </row>
-    <row r="6" spans="1:2" hidden="1">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="6" t="s">
         <v>6</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B6" xr:uid="{567EE969-C8CC-4648-B0E1-A81E0D083ADD}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="São Paulo"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Calibri"&amp;10&amp;KFF0000 Classificação: Restrito&amp;1#_x000D_</oddHeader>

--- a/Desafio 4 - Vale Refeição/Desafio 4 - Dados/BASE SINDICATO X VALOR.xlsx
+++ b/Desafio 4 - Vale Refeição/Desafio 4 - Dados/BASE SINDICATO X VALOR.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\thais.agne\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Meu Drive\Cursos e Treinamentos\Cientista de Dados\Treinamento Python\I2A2\Desafios\Desafio 4 - Vale Refeição\Desafio 4 - Dados\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A5ACCD5E-3A5E-4BAA-A3CB-47479A88C45E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DB1F6B3-CE67-4B88-8DA9-E27CE55C544A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{ACAACFC3-E98F-40BF-9B32-1921B65F1066}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{ACAACFC3-E98F-40BF-9B32-1921B65F1066}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -31,12 +31,15 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>ESTADO                                                     </t>
   </si>
@@ -55,9 +58,6 @@
   <si>
     <t>São Paulo</t>
   </si>
-  <si>
-    <t>​​​​​​</t>
-  </si>
 </sst>
 </file>
 
@@ -66,7 +66,7 @@
   <numFmts count="1">
     <numFmt numFmtId="8" formatCode="&quot;R$&quot;\ #,##0.00;[Red]\-&quot;R$&quot;\ #,##0.00"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -83,12 +83,6 @@
     </font>
     <font>
       <sz val="8"/>
-      <color rgb="FF323130"/>
-      <name val="Segoe UI"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="9"/>
       <color rgb="FF323130"/>
       <name val="Segoe UI"/>
       <family val="2"/>
@@ -147,7 +141,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -162,9 +156,6 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="8" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -502,9 +493,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{567EE969-C8CC-4648-B0E1-A81E0D083ADD}">
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultColWidth="14.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="14.125" defaultRowHeight="14.25"/>
   <sheetData>
-    <row r="1" spans="1:2" ht="23.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:2" ht="21.75" thickBot="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -512,7 +503,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:2" ht="15" thickBot="1">
       <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
@@ -520,7 +511,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:2" ht="15" thickBot="1">
       <c r="A3" s="4" t="s">
         <v>3</v>
       </c>
@@ -528,7 +519,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:2" ht="15" thickBot="1">
       <c r="A4" s="2" t="s">
         <v>4</v>
       </c>
@@ -536,7 +527,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:2" ht="15" thickBot="1">
       <c r="A5" s="4" t="s">
         <v>5</v>
       </c>
@@ -544,13 +535,13 @@
         <v>37.5</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A6" s="6" t="s">
-        <v>6</v>
-      </c>
+    <row r="6" spans="1:2" ht="15" thickBot="1">
+      <c r="A6" s="4"/>
+      <c r="B6" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Calibri"&amp;10&amp;KFF0000 Classificação: Restrito&amp;1#_x000D_</oddHeader>
   </headerFooter>
